--- a/sheets/조재수대금교본/검수/나의 하나님.xlsx
+++ b/sheets/조재수대금교본/검수/나의 하나님.xlsx
@@ -3587,7 +3587,7 @@
       <c r="J3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">淋
-–Z</t>
+–</t>
         </is>
       </c>
       <c r="K3" s="22"/>
@@ -3638,11 +3638,7 @@
         </is>
       </c>
       <c r="I4" s="23"/>
-      <c r="J4" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="J4" s="21"/>
       <c r="K4" s="23"/>
       <c r="L4" s="21" t="inlineStr">
         <is>
@@ -3673,8 +3669,7 @@
       <c r="G5" s="24"/>
       <c r="H5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-ㄴ</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I5" s="24"/>
@@ -3691,44 +3686,26 @@
       <c r="O5" s="24"/>
       <c r="P5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-ㄴ</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="Q5" s="24"/>
     </row>
     <row r="6" ht="86.26" customHeight="true">
       <c r="A6" s="0"/>
-      <c r="B6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="B6" s="21"/>
       <c r="C6" s="22"/>
-      <c r="D6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="D6" s="21"/>
       <c r="E6" s="22"/>
-      <c r="F6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="F6" s="21"/>
       <c r="G6" s="22"/>
       <c r="H6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南
-‹</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="I6" s="22"/>
-      <c r="J6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="J6" s="21"/>
       <c r="K6" s="22"/>
       <c r="L6" s="21" t="inlineStr">
         <is>
@@ -3736,11 +3713,7 @@
         </is>
       </c>
       <c r="M6" s="22"/>
-      <c r="N6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="N6" s="21"/>
       <c r="O6" s="22"/>
       <c r="P6" s="21" t="inlineStr">
         <is>
@@ -3888,8 +3861,7 @@
       <c r="M9" s="22"/>
       <c r="N9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-ㄴ</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="O9" s="22"/>
@@ -3905,42 +3877,27 @@
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林
-‹</t>
+          <t xml:space="preserve">林</t>
         </is>
       </c>
       <c r="C10" s="23"/>
-      <c r="D10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="D10" s="21"/>
       <c r="E10" s="23"/>
-      <c r="F10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="F10" s="21"/>
       <c r="G10" s="23"/>
       <c r="H10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
-‹</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="I10" s="23"/>
       <c r="J10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋
-‹</t>
+          <t xml:space="preserve">淋</t>
         </is>
       </c>
       <c r="K10" s="23"/>
-      <c r="L10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="L10" s="21"/>
       <c r="M10" s="23"/>
       <c r="N10" s="21" t="inlineStr">
         <is>
@@ -3950,8 +3907,7 @@
       <c r="O10" s="23"/>
       <c r="P10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
-‹</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="Q10" s="23"/>
@@ -4108,41 +4064,23 @@
         </is>
       </c>
       <c r="C14" s="24"/>
-      <c r="D14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="D14" s="21"/>
       <c r="E14" s="24"/>
-      <c r="F14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="F14" s="21"/>
       <c r="G14" s="24"/>
       <c r="H14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林
-‹</t>
+          <t xml:space="preserve">林</t>
         </is>
       </c>
       <c r="I14" s="24"/>
-      <c r="J14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="J14" s="21"/>
       <c r="K14" s="24"/>
-      <c r="L14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="L14" s="21"/>
       <c r="M14" s="24"/>
       <c r="N14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
-‹</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="O14" s="24"/>

--- a/sheets/조재수대금교본/검수/나의 하나님.xlsx
+++ b/sheets/조재수대금교본/검수/나의 하나님.xlsx
@@ -3587,7 +3587,7 @@
       <c r="J3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">淋
-–</t>
+–Z</t>
         </is>
       </c>
       <c r="K3" s="22"/>
@@ -3638,7 +3638,11 @@
         </is>
       </c>
       <c r="I4" s="23"/>
-      <c r="J4" s="21"/>
+      <c r="J4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="K4" s="23"/>
       <c r="L4" s="21" t="inlineStr">
         <is>
@@ -3669,7 +3673,8 @@
       <c r="G5" s="24"/>
       <c r="H5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">–
+ㄴ</t>
         </is>
       </c>
       <c r="I5" s="24"/>
@@ -3686,7 +3691,8 @@
       <c r="O5" s="24"/>
       <c r="P5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">–
+ㄴ</t>
         </is>
       </c>
       <c r="Q5" s="24"/>
@@ -3861,7 +3867,8 @@
       <c r="M9" s="22"/>
       <c r="N9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">–
+ㄴ</t>
         </is>
       </c>
       <c r="O9" s="22"/>

--- a/sheets/조재수대금교본/검수/나의 하나님.xlsx
+++ b/sheets/조재수대금교본/검수/나의 하나님.xlsx
@@ -3511,28 +3511,28 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="10.71" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="10.71" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="10.71" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="10.71" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="10.71" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="10.71" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="10.71" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="10.71" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="57.97" customHeight="true">
+    <row r="2" ht="64.52" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -3555,7 +3555,7 @@
       <c r="P2" s="20"/>
       <c r="Q2" s="20"/>
     </row>
-    <row r="3" ht="86.26" customHeight="true">
+    <row r="3" ht="96.05" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="Q3" s="22"/>
     </row>
-    <row r="4" ht="86.26" customHeight="true">
+    <row r="4" ht="96.05" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="Q4" s="23"/>
     </row>
-    <row r="5" ht="86.26" customHeight="true">
+    <row r="5" ht="96.05" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21"/>
       <c r="C5" s="24"/>
@@ -3697,7 +3697,7 @@
       </c>
       <c r="Q5" s="24"/>
     </row>
-    <row r="6" ht="86.26" customHeight="true">
+    <row r="6" ht="96.05" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21"/>
       <c r="C6" s="22"/>
@@ -3728,7 +3728,7 @@
       </c>
       <c r="Q6" s="22"/>
     </row>
-    <row r="7" ht="86.26" customHeight="true">
+    <row r="7" ht="96.05" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -3785,7 +3785,7 @@
       </c>
       <c r="Q7" s="23"/>
     </row>
-    <row r="8" ht="86.26" customHeight="true">
+    <row r="8" ht="96.05" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="Q8" s="24"/>
     </row>
-    <row r="9" ht="86.26" customHeight="true">
+    <row r="9" ht="96.05" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -3880,7 +3880,7 @@
       </c>
       <c r="Q9" s="22"/>
     </row>
-    <row r="10" ht="86.26" customHeight="true">
+    <row r="10" ht="96.05" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -3919,7 +3919,7 @@
       </c>
       <c r="Q10" s="23"/>
     </row>
-    <row r="11" ht="86.26" customHeight="true">
+    <row r="11" ht="96.05" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="Q11" s="24"/>
     </row>
-    <row r="12" ht="86.26" customHeight="true">
+    <row r="12" ht="96.05" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -4029,7 +4029,7 @@
       </c>
       <c r="Q12" s="22"/>
     </row>
-    <row r="13" ht="86.26" customHeight="true">
+    <row r="13" ht="96.05" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21"/>
       <c r="C13" s="23"/>
@@ -4063,7 +4063,7 @@
       </c>
       <c r="Q13" s="23"/>
     </row>
-    <row r="14" ht="86.26" customHeight="true">
+    <row r="14" ht="96.05" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -4105,6 +4105,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="69"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="62"/>
 </worksheet>
 </file>